--- a/testing/reports/AI_Study_Planner_UI_UX_Test.xlsx
+++ b/testing/reports/AI_Study_Planner_UI_UX_Test.xlsx
@@ -560,7 +560,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Visual Aesthetics, WCAG AA Contrast, Responsiveness &amp; Micro-animations | Executed: 2026-08-19 14:51:29</t>
+          <t>Visual Aesthetics, WCAG AA Contrast, Responsiveness &amp; Micro-animations | Executed: 2026-08-20 15:41:27</t>
         </is>
       </c>
     </row>
